--- a/data/trans_orig/P23_1_2016_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Clase-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2016</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2016 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>197807</t>
+          <t>198880</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>240529</t>
+          <t>241677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,1%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,06%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>191986</t>
+          <t>192110</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>228385</t>
+          <t>230363</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,81%</t>
+          <t>66,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>402769</t>
+          <t>399630</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>462414</t>
+          <t>458017</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,89%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,01%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>84737</t>
+          <t>85123</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120785</t>
+          <t>121177</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54320</t>
+          <t>54118</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85729</t>
+          <t>84698</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,7%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149629</t>
+          <t>149174</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196424</t>
+          <t>194482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>7933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25577</t>
+          <t>25268</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3652</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14384</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13754</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>32876</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,24%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77002</t>
+          <t>75427</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112508</t>
+          <t>112135</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,58%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45750</t>
+          <t>45967</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>75387</t>
+          <t>74152</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,12 +1120,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>131085</t>
+          <t>129126</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>178317</t>
+          <t>175598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>164757</t>
+          <t>166641</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>206072</t>
+          <t>206165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>44,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>180137</t>
+          <t>181999</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220278</t>
+          <t>220586</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>59,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>357142</t>
+          <t>360795</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>414729</t>
+          <t>417539</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>47,78%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>55,87%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69306</t>
+          <t>68901</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101675</t>
+          <t>101743</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>55891</t>
+          <t>54978</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>86580</t>
+          <t>88578</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>134362</t>
+          <t>132658</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>180469</t>
+          <t>178843</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5059</t>
+          <t>5135</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>21153</t>
+          <t>19539</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,12 +1541,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3801</t>
+          <t>3750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15281</t>
+          <t>14482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,12 +1576,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10755</t>
+          <t>10635</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30057</t>
+          <t>29112</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>77919</t>
+          <t>78210</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>111737</t>
+          <t>112192</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,71%</t>
+          <t>20,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,71%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>76686</t>
+          <t>75456</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>110462</t>
+          <t>111041</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>20,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162994</t>
+          <t>162131</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>212608</t>
+          <t>211302</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,27%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>163275</t>
+          <t>165967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210218</t>
+          <t>210640</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,28%</t>
+          <t>31,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,28%</t>
+          <t>40,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83578</t>
+          <t>83877</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109885</t>
+          <t>109568</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,15%</t>
+          <t>65,96%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260172</t>
+          <t>260234</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>310300</t>
+          <t>312401</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,1%</t>
+          <t>45,4%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99209</t>
+          <t>99205</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>135791</t>
+          <t>137937</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,02%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10011</t>
+          <t>9383</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25556</t>
+          <t>25816</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>115862</t>
+          <t>114496</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>157178</t>
+          <t>157274</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,64%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>22,86%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7464</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23071</t>
+          <t>23039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2976</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13302</t>
+          <t>13848</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12430</t>
+          <t>12617</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30650</t>
+          <t>30677</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>178636</t>
+          <t>179793</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225394</t>
+          <t>225020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,19%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35364</t>
+          <t>35042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>58691</t>
+          <t>59459</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>35,79%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>223783</t>
+          <t>224165</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>274118</t>
+          <t>276612</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,52%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,2%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>418406</t>
+          <t>419485</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>485245</t>
+          <t>485428</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,52%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>42,26%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>380376</t>
+          <t>378473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>435653</t>
+          <t>438656</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>45,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>52,81%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>817334</t>
+          <t>817045</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>905889</t>
+          <t>910430</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,41%</t>
+          <t>41,4%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>46,13%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>237059</t>
+          <t>236122</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>295514</t>
+          <t>294422</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>83016</t>
+          <t>82036</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>121607</t>
+          <t>122678</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>328487</t>
+          <t>330204</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>397852</t>
+          <t>398462</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,19%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>18919</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>42078</t>
+          <t>41619</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21721</t>
+          <t>21935</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>46418</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45592</t>
+          <t>45166</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77110</t>
+          <t>77019</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>368546</t>
+          <t>368069</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>434211</t>
+          <t>438269</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>32,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,8%</t>
+          <t>38,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>258879</t>
+          <t>259096</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>310451</t>
+          <t>313286</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,38%</t>
+          <t>31,41%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>646650</t>
+          <t>641451</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>727173</t>
+          <t>725655</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>32,5%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,84%</t>
+          <t>36,77%</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>226831</t>
+          <t>226614</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>274915</t>
+          <t>277858</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,54%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,76%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>409820</t>
+          <t>410882</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>464616</t>
+          <t>466511</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,59%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>653693</t>
+          <t>654428</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>725526</t>
+          <t>729688</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,74%</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>109392</t>
+          <t>107892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149343</t>
+          <t>149645</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,62%</t>
+          <t>17,38%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67043</t>
+          <t>67045</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101686</t>
+          <t>101886</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>184210</t>
+          <t>185429</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>237033</t>
+          <t>240435</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4975</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>17864</t>
+          <t>16945</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,12 +3248,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3729</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>14789</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3283,47 +3283,47 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
+          <t>2,01%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>17712</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>11507</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>28067</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
           <t>2,07%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>17712</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>10918</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>28326</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="W26" s="2" t="inlineStr">
-        <is>
-          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>208477</t>
+          <t>205434</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>254951</t>
+          <t>257418</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,59%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>185211</t>
+          <t>183584</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>233757</t>
+          <t>233818</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,72%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>405679</t>
+          <t>404554</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>475477</t>
+          <t>473445</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>35,02%</t>
+          <t>34,87%</t>
         </is>
       </c>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>193397</t>
+          <t>192483</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>223174</t>
+          <t>223533</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,35%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,85%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>831972</t>
+          <t>828956</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>885221</t>
+          <t>886874</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>81,99%</t>
+          <t>82,15%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1037946</t>
+          <t>1038055</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1101561</t>
+          <t>1099528</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,12 +3661,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>80,6%</t>
+          <t>80,45%</t>
         </is>
       </c>
     </row>
@@ -3689,12 +3689,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2115</t>
+          <t>2114</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>12912</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34748</t>
+          <t>34746</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62133</t>
+          <t>62367</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3744,7 +3744,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>37905</t>
+          <t>39731</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>67728</t>
+          <t>68023</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3225</t>
+          <t>3969</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15734</t>
+          <t>15414</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>7006</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>23043</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13136</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>32576</t>
+          <t>31796</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,33%</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>51377</t>
+          <t>50445</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79749</t>
+          <t>79839</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>138080</t>
+          <t>135072</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>184287</t>
+          <t>186278</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>197809</t>
+          <t>196182</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>250840</t>
+          <t>252786</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,5%</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1451127</t>
+          <t>1444397</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1564395</t>
+          <t>1563223</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,88%</t>
+          <t>42,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,23%</t>
+          <t>46,2%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2156194</t>
+          <t>2160342</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2272376</t>
+          <t>2275016</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3636960</t>
+          <t>3639634</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3806234</t>
+          <t>3816422</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4230,12 +4230,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,67%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,08%</t>
+          <t>55,23%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>658055</t>
+          <t>653910</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>758039</t>
+          <t>751744</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>347008</t>
+          <t>349214</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>423988</t>
+          <t>425286</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1027897</t>
+          <t>1030969</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1151777</t>
+          <t>1151360</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>68173</t>
+          <t>67455</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>104684</t>
+          <t>105567</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>58584</t>
+          <t>58645</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>92074</t>
+          <t>95213</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>135412</t>
+          <t>134428</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>186368</t>
+          <t>185977</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,12 +4456,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -4484,12 +4484,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1035502</t>
+          <t>1030135</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1144829</t>
+          <t>1147769</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>33,92%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>799279</t>
+          <t>794249</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>906112</t>
+          <t>896903</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,67%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1857533</t>
+          <t>1859771</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2010666</t>
+          <t>2008407</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el consumo de tabaco actual o pasado en 2023</t>
+          <t>Población según el consumo de tabaco actual o pasado en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>272982</t>
+          <t>275252</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>317741</t>
+          <t>319334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,03%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>295474</t>
+          <t>297235</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>328250</t>
+          <t>330374</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>66,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,36%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>580176</t>
+          <t>582986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>637246</t>
+          <t>641945</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,9%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>67,38%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105421</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>144252</t>
+          <t>145102</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>20,82%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,55%</t>
+          <t>28,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54296</t>
+          <t>53132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79351</t>
+          <t>77270</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>165859</t>
+          <t>164782</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212008</t>
+          <t>212982</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,25%</t>
+          <t>22,36%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3664</t>
+          <t>3429</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>14965</t>
+          <t>15049</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9877</t>
+          <t>9685</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22164</t>
+          <t>22349</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15369</t>
+          <t>15754</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32139</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63200</t>
+          <t>62034</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95265</t>
+          <t>95092</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43939</t>
+          <t>43530</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67303</t>
+          <t>67060</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>111305</t>
+          <t>112075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154142</t>
+          <t>154433</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>244201</t>
+          <t>242818</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>285750</t>
+          <t>288298</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>224308</t>
+          <t>227935</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>256735</t>
+          <t>259760</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,9%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>482359</t>
+          <t>480742</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>534183</t>
+          <t>534956</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>63,99%</t>
+          <t>64,08%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>78715</t>
+          <t>77568</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>110717</t>
+          <t>111291</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45805</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69837</t>
+          <t>69312</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>11,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130467</t>
+          <t>130927</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170116</t>
+          <t>172080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,63%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>20,61%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5382</t>
+          <t>5742</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29837</t>
+          <t>33725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7546</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20568</t>
+          <t>19568</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15840</t>
+          <t>15021</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43672</t>
+          <t>43348</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,19%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>63136</t>
+          <t>64755</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>97752</t>
+          <t>98992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>59598</t>
+          <t>57324</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>87209</t>
+          <t>85666</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>14,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>129583</t>
+          <t>130733</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>172592</t>
+          <t>173496</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,78%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>71820</t>
+          <t>82343</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>334514</t>
+          <t>338605</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,06%</t>
+          <t>50,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>108603</t>
+          <t>110512</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>127821</t>
+          <t>128333</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>66,21%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>135861</t>
+          <t>142456</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>471784</t>
+          <t>470121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,29%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>145699</t>
+          <t>142915</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>549616</t>
+          <t>534936</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>82,25%</t>
+          <t>80,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15834</t>
+          <t>15628</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29845</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>158986</t>
+          <t>159355</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>637395</t>
+          <t>614633</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>76,32%</t>
+          <t>73,59%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1387</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20208</t>
+          <t>20572</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5423</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6367,7 +6367,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2916</t>
+          <t>3079</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21421</t>
+          <t>22253</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>42696</t>
+          <t>45723</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>186121</t>
+          <t>187054</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,84%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17308</t>
+          <t>17476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31661</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,97%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>57372</t>
+          <t>68933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>197814</t>
+          <t>199552</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,89%</t>
         </is>
       </c>
     </row>
@@ -6655,12 +6655,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>469242</t>
+          <t>469445</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>540097</t>
+          <t>541766</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6670,12 +6670,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>52,35%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6690,12 +6690,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>599765</t>
+          <t>598107</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>815093</t>
+          <t>826948</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1082380</t>
+          <t>1082641</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1457827</t>
+          <t>1481710</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>73,63%</t>
         </is>
       </c>
     </row>
@@ -6768,12 +6768,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>167095</t>
+          <t>166445</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>213611</t>
+          <t>214773</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -6783,12 +6783,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6803,12 +6803,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>39203</t>
+          <t>42344</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>103252</t>
+          <t>105540</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>185504</t>
+          <t>182589</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>310813</t>
+          <t>312362</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,52%</t>
         </is>
       </c>
     </row>
@@ -6881,12 +6881,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>14042</t>
+          <t>13678</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>38062</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6896,12 +6896,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6916,12 +6916,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7834</t>
+          <t>7467</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>27292</t>
+          <t>26961</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6931,12 +6931,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6951,12 +6951,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57667</t>
+          <t>57996</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6966,12 +6966,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,88%</t>
         </is>
       </c>
     </row>
@@ -6994,12 +6994,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>277633</t>
+          <t>280011</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>347783</t>
+          <t>354554</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7009,12 +7009,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7029,12 +7029,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>108939</t>
+          <t>97541</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>256711</t>
+          <t>256308</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7044,12 +7044,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7064,12 +7064,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>342873</t>
+          <t>326354</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>585918</t>
+          <t>584996</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7079,12 +7079,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>17,04%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,07%</t>
         </is>
       </c>
     </row>
@@ -7224,12 +7224,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>202379</t>
+          <t>203861</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>247264</t>
+          <t>249317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -7239,12 +7239,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,01%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>574612</t>
+          <t>575141</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>667111</t>
+          <t>670640</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -7274,12 +7274,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7294,12 +7294,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>788109</t>
+          <t>790300</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>919274</t>
+          <t>925453</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>59,95%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,39%</t>
         </is>
       </c>
     </row>
@@ -7337,12 +7337,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73643</t>
+          <t>73658</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>105612</t>
+          <t>107417</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7372,12 +7372,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>51026</t>
+          <t>52801</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>87795</t>
+          <t>89566</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -7387,12 +7387,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7407,12 +7407,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130292</t>
+          <t>130134</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>185427</t>
+          <t>183253</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -7422,12 +7422,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>13,94%</t>
         </is>
       </c>
     </row>
@@ -7450,12 +7450,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1244</t>
+          <t>1323</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10141</t>
+          <t>10186</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -7465,12 +7465,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7485,12 +7485,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>7039</t>
+          <t>6993</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17568</t>
+          <t>17856</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -7500,12 +7500,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7520,12 +7520,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10356</t>
+          <t>10268</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23338</t>
+          <t>24594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -7535,12 +7535,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -7563,12 +7563,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>134243</t>
+          <t>133555</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>177886</t>
+          <t>177689</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -7578,12 +7578,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7598,12 +7598,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>111373</t>
+          <t>110765</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>174634</t>
+          <t>173560</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -7613,12 +7613,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7633,12 +7633,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>247102</t>
+          <t>249543</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>340291</t>
+          <t>340321</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -7648,12 +7648,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>25,89%</t>
         </is>
       </c>
     </row>
@@ -7793,12 +7793,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>179854</t>
+          <t>181820</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>216993</t>
+          <t>219329</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7808,12 +7808,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,09%</t>
+          <t>75,92%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>90,6%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7828,12 +7828,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>616139</t>
+          <t>617689</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>657737</t>
+          <t>655851</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7843,12 +7843,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>81,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>86,14%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7863,12 +7863,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>808658</t>
+          <t>811357</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>863383</t>
+          <t>866779</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7878,12 +7878,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,6%</t>
         </is>
       </c>
     </row>
@@ -7906,12 +7906,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2520</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16279</t>
+          <t>16151</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7921,12 +7921,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7941,12 +7941,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28535</t>
+          <t>28128</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>50186</t>
+          <t>49088</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7956,12 +7956,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7976,12 +7976,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>33945</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>58187</t>
+          <t>59754</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7991,12 +7991,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,97%</t>
         </is>
       </c>
     </row>
@@ -8019,12 +8019,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>36506</t>
+          <t>31655</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -8034,12 +8034,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8054,12 +8054,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4101</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22879</t>
+          <t>22344</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -8069,12 +8069,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8089,12 +8089,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>11945</t>
+          <t>10699</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>44312</t>
+          <t>45598</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -8104,12 +8104,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,56%</t>
         </is>
       </c>
     </row>
@@ -8132,12 +8132,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6409</t>
+          <t>6622</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29296</t>
+          <t>29056</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8167,12 +8167,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>61640</t>
+          <t>61411</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>92767</t>
+          <t>92877</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -8182,12 +8182,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8202,12 +8202,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>73034</t>
+          <t>73109</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>112742</t>
+          <t>113769</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -8222,7 +8222,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -8362,12 +8362,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1335602</t>
+          <t>1213917</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1860580</t>
+          <t>1863706</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -8377,12 +8377,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>35,98%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2526470</t>
+          <t>2520649</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2790810</t>
+          <t>2777168</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -8412,12 +8412,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,48%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3804321</t>
+          <t>3752416</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4556569</t>
+          <t>4544114</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -8447,12 +8447,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>53,99%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,56%</t>
+          <t>65,38%</t>
         </is>
       </c>
     </row>
@@ -8475,12 +8475,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>632146</t>
+          <t>633550</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1411059</t>
+          <t>1579480</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>268219</t>
+          <t>275929</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>368295</t>
+          <t>371422</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -8525,12 +8525,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>940369</t>
+          <t>939241</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>2024794</t>
+          <t>1947035</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -8560,12 +8560,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,53%</t>
+          <t>13,51%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>29,13%</t>
+          <t>28,01%</t>
         </is>
       </c>
     </row>
@@ -8588,12 +8588,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50539</t>
+          <t>48407</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>98603</t>
+          <t>100540</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>51665</t>
+          <t>53053</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>85552</t>
+          <t>87929</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8658,12 +8658,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>108666</t>
+          <t>111716</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>173008</t>
+          <t>173065</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -8673,7 +8673,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -8701,12 +8701,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>583167</t>
+          <t>537322</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>832880</t>
+          <t>831547</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,69%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8736,12 +8736,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>464658</t>
+          <t>469093</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>623664</t>
+          <t>626768</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -8751,12 +8751,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8771,12 +8771,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1118370</t>
+          <t>1142683</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1428504</t>
+          <t>1432080</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P23_1_2016_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P23_1_2016_2023-Clase-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>198880</t>
+          <t>197466</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>241677</t>
+          <t>240418</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,02%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>192110</t>
+          <t>192023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>230363</t>
+          <t>230344</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>66,38%</t>
+          <t>66,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>399630</t>
+          <t>406371</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>458017</t>
+          <t>462460</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>59,58%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85123</t>
+          <t>85299</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>121177</t>
+          <t>123595</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>19,84%</t>
+          <t>19,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>28,8%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>54118</t>
+          <t>53320</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>84698</t>
+          <t>85451</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>149174</t>
+          <t>146196</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>194482</t>
+          <t>196092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>25,06%</t>
+          <t>25,26%</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>7374</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25268</t>
+          <t>24150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -972,12 +972,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>13918</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>13716</t>
+          <t>13385</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32876</t>
+          <t>31751</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -1070,12 +1070,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>75427</t>
+          <t>76153</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>112135</t>
+          <t>112610</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1085,12 +1085,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1105,12 +1105,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45967</t>
+          <t>46234</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>74152</t>
+          <t>74168</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1140,12 +1140,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>129126</t>
+          <t>130099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>175598</t>
+          <t>175837</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1155,12 +1155,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -1300,12 +1300,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>166641</t>
+          <t>167425</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>206165</t>
+          <t>205073</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1315,12 +1315,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,3%</t>
+          <t>44,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181999</t>
+          <t>181101</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>220586</t>
+          <t>219346</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1350,12 +1350,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1370,12 +1370,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>360795</t>
+          <t>356979</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>417539</t>
+          <t>414703</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>55,87%</t>
+          <t>55,49%</t>
         </is>
       </c>
     </row>
@@ -1413,12 +1413,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>68901</t>
+          <t>69222</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>101743</t>
+          <t>102901</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,36%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1448,12 +1448,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>54978</t>
+          <t>56023</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>88578</t>
+          <t>86285</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1463,12 +1463,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>15,09%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1483,12 +1483,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>132658</t>
+          <t>133569</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>178843</t>
+          <t>177709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1498,12 +1498,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>23,78%</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5135</t>
+          <t>5216</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19539</t>
+          <t>19504</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1561,12 +1561,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3750</t>
+          <t>3807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14482</t>
+          <t>14493</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1596,12 +1596,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10635</t>
+          <t>11576</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29112</t>
+          <t>30496</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1611,12 +1611,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>78210</t>
+          <t>78578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>112192</t>
+          <t>114440</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1674,12 +1674,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75456</t>
+          <t>76777</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>111041</t>
+          <t>109448</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>29,91%</t>
+          <t>29,48%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1709,12 +1709,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>162131</t>
+          <t>164405</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>211302</t>
+          <t>213254</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1724,12 +1724,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>28,53%</t>
         </is>
       </c>
     </row>
@@ -1869,12 +1869,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>165967</t>
+          <t>166005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>210640</t>
+          <t>210804</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1884,12 +1884,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,36%</t>
+          <t>40,39%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1904,12 +1904,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>83877</t>
+          <t>83958</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109568</t>
+          <t>110235</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1919,12 +1919,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,96%</t>
+          <t>66,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1939,12 +1939,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>260234</t>
+          <t>257781</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>312401</t>
+          <t>311050</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>37,82%</t>
+          <t>37,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,21%</t>
         </is>
       </c>
     </row>
@@ -1982,12 +1982,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>99205</t>
+          <t>98446</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>137937</t>
+          <t>140139</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1997,12 +1997,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2017,12 +2017,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9383</t>
+          <t>9813</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25816</t>
+          <t>26238</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2032,12 +2032,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2052,12 +2052,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>114496</t>
+          <t>114280</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>157274</t>
+          <t>155996</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,61%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,67%</t>
         </is>
       </c>
     </row>
@@ -2095,12 +2095,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7711</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23039</t>
+          <t>21941</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,12 +2110,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2130,12 +2130,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>2128</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13848</t>
+          <t>13898</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2145,12 +2145,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12617</t>
+          <t>12370</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>30677</t>
+          <t>32153</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>179793</t>
+          <t>180886</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>225020</t>
+          <t>228338</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2223,12 +2223,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>34,45%</t>
+          <t>34,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2243,12 +2243,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>35042</t>
+          <t>35246</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>59459</t>
+          <t>58973</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2258,12 +2258,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>35,79%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2278,12 +2278,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>224165</t>
+          <t>222781</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>276612</t>
+          <t>275980</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,38%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>40,11%</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>419485</t>
+          <t>420804</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>485428</t>
+          <t>489036</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2453,12 +2453,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2473,12 +2473,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>378473</t>
+          <t>379913</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>438656</t>
+          <t>436386</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>46,05%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2508,12 +2508,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>817045</t>
+          <t>819346</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>910430</t>
+          <t>903661</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2523,12 +2523,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>45,78%</t>
         </is>
       </c>
     </row>
@@ -2551,12 +2551,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>236122</t>
+          <t>235052</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>294422</t>
+          <t>295426</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>25,63%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>82036</t>
+          <t>80907</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>122678</t>
+          <t>119332</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2621,12 +2621,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>330204</t>
+          <t>329026</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>398462</t>
+          <t>404296</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -2664,12 +2664,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18919</t>
+          <t>18681</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41619</t>
+          <t>39534</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2679,12 +2679,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>21935</t>
+          <t>21791</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>45855</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2734,12 +2734,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>45166</t>
+          <t>44828</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>77019</t>
+          <t>75885</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
     </row>
@@ -2777,12 +2777,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>368069</t>
+          <t>368853</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>438269</t>
+          <t>434975</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,04%</t>
+          <t>32,11%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>38,15%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2812,12 +2812,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>259096</t>
+          <t>256277</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>313286</t>
+          <t>313277</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,41%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -2847,12 +2847,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>641451</t>
+          <t>647373</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>725655</t>
+          <t>728987</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>36,93%</t>
         </is>
       </c>
     </row>
@@ -3007,12 +3007,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>226614</t>
+          <t>228063</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>277858</t>
+          <t>277690</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3022,12 +3022,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,74%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3042,12 +3042,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>410882</t>
+          <t>412151</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>466511</t>
+          <t>462705</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>62,77%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3077,12 +3077,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>654428</t>
+          <t>652967</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>729688</t>
+          <t>728325</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>48,09%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,64%</t>
         </is>
       </c>
     </row>
@@ -3120,12 +3120,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>107892</t>
+          <t>108456</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>149645</t>
+          <t>148701</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3135,12 +3135,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>17,38%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,12 +3155,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>67045</t>
+          <t>66891</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>101886</t>
+          <t>102186</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>185429</t>
+          <t>185629</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>240435</t>
+          <t>239334</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,63%</t>
         </is>
       </c>
     </row>
@@ -3233,12 +3233,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4975</t>
+          <t>4875</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>16945</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3248,82 +3248,82 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>7989</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>3068</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>15176</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>0,42%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>2,06%</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
+        <is>
+          <t>17712</t>
+        </is>
+      </c>
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>10809</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>27825</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
           <t>0,8%</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>7989</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>3858</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>14789</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>2,01%</t>
-        </is>
-      </c>
-      <c r="Q26" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="R26" s="2" t="inlineStr">
-        <is>
-          <t>17712</t>
-        </is>
-      </c>
-      <c r="S26" s="2" t="inlineStr">
-        <is>
-          <t>11507</t>
-        </is>
-      </c>
-      <c r="T26" s="2" t="inlineStr">
-        <is>
-          <t>28067</t>
-        </is>
-      </c>
-      <c r="U26" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="V26" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,05%</t>
         </is>
       </c>
     </row>
@@ -3346,12 +3346,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>205434</t>
+          <t>208784</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>257418</t>
+          <t>254892</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,64%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>41,47%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>183584</t>
+          <t>184521</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>233818</t>
+          <t>234173</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3396,12 +3396,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,03%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>31,72%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>404554</t>
+          <t>404942</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>473445</t>
+          <t>473025</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3431,12 +3431,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>34,84%</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3556,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3576,12 +3576,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>192483</t>
+          <t>192963</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>223533</t>
+          <t>224753</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3591,12 +3591,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>78,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3611,12 +3611,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>828956</t>
+          <t>834454</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>886874</t>
+          <t>886408</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3626,12 +3626,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>76,78%</t>
+          <t>77,29%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>82,15%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3646,12 +3646,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>1038055</t>
+          <t>1039996</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>1099528</t>
+          <t>1099629</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3661,7 +3661,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>76,09%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3689,12 +3689,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2114</t>
+          <t>2111</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>12016</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3709,7 +3709,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>34746</t>
+          <t>34602</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>62367</t>
+          <t>61928</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3739,12 +3739,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>39731</t>
+          <t>40395</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>68023</t>
+          <t>70448</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3774,12 +3774,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -3802,12 +3802,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3969</t>
+          <t>3212</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>15414</t>
+          <t>15371</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>6559</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22754</t>
+          <t>21880</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3852,12 +3852,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>13341</t>
+          <t>12881</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>31796</t>
+          <t>32298</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3887,12 +3887,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>50445</t>
+          <t>49571</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>79839</t>
+          <t>77888</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3930,12 +3930,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>27,8%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3950,12 +3950,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>135072</t>
+          <t>137649</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>186278</t>
+          <t>182552</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,75%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>17,25%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3985,12 +3985,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>196182</t>
+          <t>194906</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>252786</t>
+          <t>250271</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4000,12 +4000,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,31%</t>
         </is>
       </c>
     </row>
@@ -4145,12 +4145,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1444397</t>
+          <t>1455745</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1563223</t>
+          <t>1569411</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4160,12 +4160,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>46,2%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2160342</t>
+          <t>2162880</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2275016</t>
+          <t>2277657</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4195,12 +4195,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>61,27%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,59%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3639634</t>
+          <t>3639355</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>3816422</t>
+          <t>3810108</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4235,7 +4235,7 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,14%</t>
         </is>
       </c>
     </row>
@@ -4258,12 +4258,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>653910</t>
+          <t>661764</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>751744</t>
+          <t>759549</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4273,12 +4273,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>22,45%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4293,12 +4293,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>349214</t>
+          <t>352023</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>425286</t>
+          <t>428245</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4308,12 +4308,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>12,06%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4328,12 +4328,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>1030969</t>
+          <t>1026421</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1151360</t>
+          <t>1144408</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4343,12 +4343,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>16,56%</t>
         </is>
       </c>
     </row>
@@ -4371,12 +4371,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>67455</t>
+          <t>67517</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>105567</t>
+          <t>104276</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4386,12 +4386,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4406,12 +4406,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>58645</t>
+          <t>58715</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>95213</t>
+          <t>93904</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4421,12 +4421,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>134428</t>
+          <t>136871</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>185977</t>
+          <t>185948</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1030135</t>
+          <t>1032184</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1147769</t>
+          <t>1140170</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4499,12 +4499,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>33,92%</t>
+          <t>33,7%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4519,12 +4519,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>794249</t>
+          <t>797943</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>896903</t>
+          <t>897300</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4534,12 +4534,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4554,12 +4554,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1859771</t>
+          <t>1860380</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>2008407</t>
+          <t>2011968</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4569,12 +4569,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,12%</t>
         </is>
       </c>
     </row>
@@ -4943,32 +4943,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>296943</t>
+          <t>325718</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>275252</t>
+          <t>300596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>319334</t>
+          <t>348741</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>54,48%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>63,21%</t>
+          <t>63,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4978,32 +4978,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>313258</t>
+          <t>345822</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>297235</t>
+          <t>327457</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>330374</t>
+          <t>362836</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5013,27 +5013,27 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>610201</t>
+          <t>671540</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>582986</t>
+          <t>642650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>641945</t>
+          <t>700139</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>64,05%</t>
+          <t>64,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -5056,32 +5056,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>123377</t>
+          <t>130620</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>105202</t>
+          <t>108770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145102</t>
+          <t>149858</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5091,32 +5091,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>65031</t>
+          <t>69425</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>53132</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>77270</t>
+          <t>83326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5126,32 +5126,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>188408</t>
+          <t>200044</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>164782</t>
+          <t>176732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>212982</t>
+          <t>226570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>17,3%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>21,81%</t>
         </is>
       </c>
     </row>
@@ -5169,32 +5169,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>7737</t>
+          <t>8936</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3429</t>
+          <t>4279</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15049</t>
+          <t>16690</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5204,32 +5204,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>15157</t>
+          <t>15891</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>9685</t>
+          <t>10621</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>22349</t>
+          <t>23430</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5239,32 +5239,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>22894</t>
+          <t>24828</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15754</t>
+          <t>16609</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>34682</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,34%</t>
         </is>
       </c>
     </row>
@@ -5282,32 +5282,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>77155</t>
+          <t>85344</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>62034</t>
+          <t>69133</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95092</t>
+          <t>103657</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5317,32 +5317,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>54021</t>
+          <t>57273</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43530</t>
+          <t>46342</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67060</t>
+          <t>71328</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,99%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5352,22 +5352,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>131176</t>
+          <t>142618</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>112075</t>
+          <t>122235</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>154433</t>
+          <t>164697</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -5395,17 +5395,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>505212</t>
+          <t>550618</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5430,17 +5430,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>447467</t>
+          <t>488411</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5465,17 +5465,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>952679</t>
+          <t>1039029</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5512,32 +5512,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>266210</t>
+          <t>286061</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>242818</t>
+          <t>262111</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>288298</t>
+          <t>306373</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>58,87%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>53,7%</t>
+          <t>54,24%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5547,32 +5547,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>242454</t>
+          <t>267797</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>227935</t>
+          <t>250182</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>259760</t>
+          <t>285354</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>63,37%</t>
+          <t>63,29%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>59,58%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5582,32 +5582,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>508663</t>
+          <t>553859</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>480742</t>
+          <t>523062</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>534956</t>
+          <t>581504</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>64,08%</t>
+          <t>64,16%</t>
         </is>
       </c>
     </row>
@@ -5625,32 +5625,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>93286</t>
+          <t>102351</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>77568</t>
+          <t>86744</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111291</t>
+          <t>121212</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,61%</t>
+          <t>25,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5660,32 +5660,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56721</t>
+          <t>62836</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45662</t>
+          <t>50677</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69312</t>
+          <t>76383</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5695,32 +5695,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>150007</t>
+          <t>165188</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>130927</t>
+          <t>144080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172080</t>
+          <t>187900</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,73%</t>
         </is>
       </c>
     </row>
@@ -5738,32 +5738,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13106</t>
+          <t>10919</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5742</t>
+          <t>4757</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33725</t>
+          <t>24020</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5773,32 +5773,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>12110</t>
+          <t>13232</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7715</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19568</t>
+          <t>20390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5808,32 +5808,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>25216</t>
+          <t>24150</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15021</t>
+          <t>14906</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>43348</t>
+          <t>36824</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -5851,32 +5851,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>79611</t>
+          <t>83881</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>64755</t>
+          <t>68771</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>98992</t>
+          <t>102747</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,89%</t>
+          <t>21,26%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>71295</t>
+          <t>79278</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>57324</t>
+          <t>66473</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>85666</t>
+          <t>94782</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5921,32 +5921,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>150906</t>
+          <t>163158</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>130733</t>
+          <t>139757</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173496</t>
+          <t>187140</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>15,66%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>20,78%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -5964,17 +5964,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5999,17 +5999,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6034,17 +6034,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6081,32 +6081,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>207587</t>
+          <t>237819</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82343</t>
+          <t>216954</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>338605</t>
+          <t>261887</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6116,32 +6116,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>119611</t>
+          <t>137482</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>110512</t>
+          <t>126386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128333</t>
+          <t>147258</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>73,32%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,89%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6151,32 +6151,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>327198</t>
+          <t>375301</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>142456</t>
+          <t>351753</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>470121</t>
+          <t>399968</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>56,94%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>60,68%</t>
         </is>
       </c>
     </row>
@@ -6194,32 +6194,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>340616</t>
+          <t>106179</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>142915</t>
+          <t>88738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>534936</t>
+          <t>123390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -6229,32 +6229,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21808</t>
+          <t>22682</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15628</t>
+          <t>15731</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>30755</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -6264,32 +6264,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>362424</t>
+          <t>128860</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>159355</t>
+          <t>110383</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>614633</t>
+          <t>149645</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>22,7%</t>
         </is>
       </c>
     </row>
@@ -6307,32 +6307,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>8673</t>
+          <t>9190</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>3820</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>18437</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6342,32 +6342,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>2022</t>
+          <t>2113</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>637</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5423</t>
+          <t>5250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6377,32 +6377,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>10695</t>
+          <t>11302</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>3079</t>
+          <t>5520</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22253</t>
+          <t>20881</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>3,17%</t>
         </is>
       </c>
     </row>
@@ -6420,32 +6420,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>111388</t>
+          <t>118425</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>45723</t>
+          <t>98802</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>187054</t>
+          <t>138231</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6455,32 +6455,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>23469</t>
+          <t>25221</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>17476</t>
+          <t>18216</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31172</t>
+          <t>33787</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6490,32 +6490,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>134858</t>
+          <t>143646</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68933</t>
+          <t>122477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>199552</t>
+          <t>165171</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,89%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -6533,17 +6533,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6568,17 +6568,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166911</t>
+          <t>187497</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6603,17 +6603,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>835175</t>
+          <t>659109</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6650,32 +6650,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>506088</t>
+          <t>556527</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>469445</t>
+          <t>518984</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>541766</t>
+          <t>593579</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>45,85%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>52,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6685,32 +6685,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>684198</t>
+          <t>543710</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>598107</t>
+          <t>519029</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>826948</t>
+          <t>567920</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>70,0%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6720,32 +6720,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1190286</t>
+          <t>1100238</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1082641</t>
+          <t>1054683</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1481710</t>
+          <t>1142952</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>55,22%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>73,63%</t>
+          <t>57,37%</t>
         </is>
       </c>
     </row>
@@ -6763,32 +6763,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>190253</t>
+          <t>212025</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>166445</t>
+          <t>187074</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>214773</t>
+          <t>238504</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>20,75%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -6798,32 +6798,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>78977</t>
+          <t>85111</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>42344</t>
+          <t>70245</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>105540</t>
+          <t>101199</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6833,32 +6833,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>269231</t>
+          <t>297136</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182589</t>
+          <t>270114</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>312362</t>
+          <t>330929</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -6876,32 +6876,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>23119</t>
+          <t>29876</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13678</t>
+          <t>18918</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>46052</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6911,32 +6911,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>20568</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>7467</t>
+          <t>12796</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>26961</t>
+          <t>30197</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6946,32 +6946,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>40495</t>
+          <t>50444</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>26011</t>
+          <t>37340</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>57996</t>
+          <t>69158</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -6989,32 +6989,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>315359</t>
+          <t>333415</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>280011</t>
+          <t>299478</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>354554</t>
+          <t>368008</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,46%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7024,32 +7024,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>196880</t>
+          <t>211120</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>97541</t>
+          <t>186687</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>256308</t>
+          <t>235170</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7059,32 +7059,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>512238</t>
+          <t>544534</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>326354</t>
+          <t>505257</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>584996</t>
+          <t>588064</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>25,36%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>29,52%</t>
         </is>
       </c>
     </row>
@@ -7102,17 +7102,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -7137,17 +7137,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977431</t>
+          <t>860509</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -7172,17 +7172,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012250</t>
+          <t>1992352</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -7219,32 +7219,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>226423</t>
+          <t>288153</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>203861</t>
+          <t>262928</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>249317</t>
+          <t>314905</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>46,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -7254,32 +7254,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>611265</t>
+          <t>575582</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>575141</t>
+          <t>551869</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>670640</t>
+          <t>598497</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>72,71%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>66,48%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>79,78%</t>
+          <t>72,1%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -7289,32 +7289,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>837688</t>
+          <t>863735</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>790300</t>
+          <t>829357</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>925453</t>
+          <t>900370</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>61,83%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>60,11%</t>
+          <t>59,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>64,45%</t>
         </is>
       </c>
     </row>
@@ -7332,32 +7332,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>88896</t>
+          <t>95144</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>73658</t>
+          <t>78994</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107417</t>
+          <t>115122</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,66%</t>
+          <t>20,31%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -7367,32 +7367,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>70710</t>
+          <t>80468</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52801</t>
+          <t>67063</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89566</t>
+          <t>96798</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -7402,32 +7402,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>159606</t>
+          <t>175612</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>130134</t>
+          <t>154438</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>183253</t>
+          <t>197412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>14,13%</t>
         </is>
       </c>
     </row>
@@ -7445,32 +7445,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>4326</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1323</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>10186</t>
+          <t>19451</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,39%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -7480,32 +7480,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>11667</t>
+          <t>14535</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6993</t>
+          <t>8661</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>17856</t>
+          <t>21249</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -7515,32 +7515,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15993</t>
+          <t>21932</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>13993</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24594</t>
+          <t>35145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -7558,32 +7558,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>154371</t>
+          <t>176188</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>133555</t>
+          <t>152784</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>177689</t>
+          <t>201398</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>28,18%</t>
+          <t>26,95%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -7593,32 +7593,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>147012</t>
+          <t>159560</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>110765</t>
+          <t>140087</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>173560</t>
+          <t>179559</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>17,49%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>16,87%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>20,65%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -7628,32 +7628,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>301383</t>
+          <t>335748</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>249543</t>
+          <t>303034</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>340321</t>
+          <t>366115</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>24,03%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>26,21%</t>
         </is>
       </c>
     </row>
@@ -7671,17 +7671,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>474016</t>
+          <t>566882</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7706,17 +7706,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>840654</t>
+          <t>830145</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7741,17 +7741,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1314670</t>
+          <t>1397026</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -7788,32 +7788,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>203447</t>
+          <t>202445</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>181820</t>
+          <t>183807</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>219329</t>
+          <t>215821</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,92%</t>
+          <t>77,86%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7823,32 +7823,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>638065</t>
+          <t>714542</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>617689</t>
+          <t>690145</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>655851</t>
+          <t>731430</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,63%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>81,13%</t>
+          <t>81,74%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>86,14%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7858,32 +7858,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>841512</t>
+          <t>916988</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>811357</t>
+          <t>885734</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>866779</t>
+          <t>941301</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>87,13%</t>
         </is>
       </c>
     </row>
@@ -7901,32 +7901,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6978</t>
+          <t>6666</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2520</t>
+          <t>2448</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>16151</t>
+          <t>14762</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7936,32 +7936,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>37254</t>
+          <t>38167</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>28128</t>
+          <t>29304</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>49088</t>
+          <t>49634</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7971,32 +7971,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>44232</t>
+          <t>44833</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>34503</t>
+          <t>34545</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>59754</t>
+          <t>58056</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -8014,32 +8014,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>3652</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>31655</t>
+          <t>30287</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -8049,32 +8049,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>10395</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>4721</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>22344</t>
+          <t>21906</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -8084,22 +8084,22 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>24013</t>
+          <t>22187</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10699</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>43897</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
@@ -8109,7 +8109,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,06%</t>
         </is>
       </c>
     </row>
@@ -8127,32 +8127,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>15101</t>
+          <t>15183</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>6622</t>
+          <t>7233</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>29056</t>
+          <t>30634</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -8162,32 +8162,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>76016</t>
+          <t>81176</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>61411</t>
+          <t>67170</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>92877</t>
+          <t>102932</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -8197,32 +8197,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>91118</t>
+          <t>96360</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>73109</t>
+          <t>79346</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>113769</t>
+          <t>119217</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,03%</t>
         </is>
       </c>
     </row>
@@ -8240,17 +8240,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>239504</t>
+          <t>236086</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -8275,17 +8275,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -8310,17 +8310,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1000875</t>
+          <t>1080367</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -8357,32 +8357,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>1706697</t>
+          <t>1896723</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>1213917</t>
+          <t>1832062</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1863706</t>
+          <t>1963289</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>55,13%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>35,98%</t>
+          <t>53,25%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -8392,32 +8392,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>2608851</t>
+          <t>2584935</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2520649</t>
+          <t>2535377</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>2777168</t>
+          <t>2633429</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -8427,32 +8427,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>4315547</t>
+          <t>4481658</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>3752416</t>
+          <t>4404142</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>4544114</t>
+          <t>4561011</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>63,35%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>53,99%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>65,38%</t>
+          <t>64,47%</t>
         </is>
       </c>
     </row>
@@ -8470,32 +8470,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>843407</t>
+          <t>652984</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>633550</t>
+          <t>610113</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1579480</t>
+          <t>702416</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>25,0%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,81%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -8505,32 +8505,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>330501</t>
+          <t>358689</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>275929</t>
+          <t>326121</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>371422</t>
+          <t>390970</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -8540,32 +8540,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>1173908</t>
+          <t>1011673</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>939241</t>
+          <t>956653</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>1947035</t>
+          <t>1064724</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>28,01%</t>
+          <t>15,05%</t>
         </is>
       </c>
     </row>
@@ -8583,32 +8583,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>70939</t>
+          <t>78110</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>48407</t>
+          <t>57651</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>100540</t>
+          <t>105652</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -8618,32 +8618,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>68368</t>
+          <t>76733</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>53053</t>
+          <t>62783</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>87929</t>
+          <t>96613</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -8653,32 +8653,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>139307</t>
+          <t>154843</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>111716</t>
+          <t>128894</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>173065</t>
+          <t>187266</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -8696,32 +8696,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>752985</t>
+          <t>812435</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>537322</t>
+          <t>757005</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>831547</t>
+          <t>870010</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -8731,32 +8731,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>568694</t>
+          <t>613628</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>469093</t>
+          <t>574163</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>626768</t>
+          <t>655938</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -8766,32 +8766,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>1321679</t>
+          <t>1426063</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>1142683</t>
+          <t>1355520</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1432080</t>
+          <t>1495315</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>20,16%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>16,44%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -8809,17 +8809,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3374028</t>
+          <t>3440252</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -8844,17 +8844,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3576414</t>
+          <t>3633985</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -8879,17 +8879,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6950441</t>
+          <t>7074237</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
